--- a/vystupy/4OG_soupis.xlsx
+++ b/vystupy/4OG_soupis.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Potrubí dle hladin" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Otopná tělesa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DN popisky" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Popisy dispozice" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Poznámky" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Potrubí dle hladin" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Otopná tělesa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="DN popisky" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Popisy dispozice" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,6 +421,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Téma</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Poznámka</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zdroj</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DXF výkres (jednotky mm). Hodnoty vytěženy automaticky skriptem tools/make_soupis.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Délky potrubí</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Součet délek LINE/ARC/SPLINE a otevřených polylinií na hladinách 'Heiz…'. Uzavřené polylinie, kružnice a elipsy vyřazeny (symboly těles/armatur). Jde o délku kresby, ne o ověřenou délku trubek.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kontrola V/R</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>U procesních okruhů přívod a zpátečka délkou sedí. U okruhů k otopným tělesům může být přívod nadhodnocen (symboly kreslené čarami na hladině přívodu) – ověřit ve výkresu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Výkon těles</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Párováno k nejbližšímu popisku 'P ≈ … W' (typicky 750 mm pod názvem; vzdálenost uvedena pro kontrolu). U '3x …' NENÍ ověřeno, zda výkon platí na kus, nebo celkem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Označení těles</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Význam čísel (např. 42/900/100 = články/výška/hloubka?) není ověřen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DN popisky</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pouze textové popisky s polohou; přiřazení ke konkrétnímu úseku potrubí nebylo provedeno.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -472,7 +575,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
@@ -493,7 +596,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
         <v>13.4</v>
@@ -514,7 +617,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
         <v>84</v>
@@ -535,7 +638,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E5" t="n">
         <v>78.5</v>
@@ -556,7 +659,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -577,7 +680,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
         <v>15.6</v>
@@ -598,7 +701,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -619,7 +722,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
         <v>20.8</v>
@@ -637,7 +740,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
         <v>20.2</v>
@@ -648,7 +751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -870,7 +973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1569,7 +1672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/vystupy/4OG_soupis.xlsx
+++ b/vystupy/4OG_soupis.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Párováno k nejbližšímu popisku 'P ≈ … W' (typicky 750 mm pod názvem; vzdálenost uvedena pro kontrolu). U '3x …' NENÍ ověřeno, zda výkon platí na kus, nebo celkem.</t>
+          <t>Párováno k nejbližšímu popisku 'P ≈ … W'. POTVRZENO (uživatel, 2026-10-06): výkon v popisku platí na 1 kus; u '3x …' je celkový výkon = počet × výkon. Viz sloupec 'Výkon celkem W'.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Výkon W (nejbližší popisek P≈)</t>
+          <t>Výkon W na 1 kus (potvrzeno uživatelem)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -803,6 +803,11 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hladina</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Výkon celkem W (počet × výkon/ks)</t>
         </is>
       </c>
     </row>
@@ -832,6 +837,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H2" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -859,6 +867,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>2300</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -886,6 +897,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H4" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -913,6 +927,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H5" t="n">
+        <v>350</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -940,6 +957,9 @@
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
       </c>
+      <c r="H6" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -966,6 +986,9 @@
         <is>
           <t>Heiz Wasser +60 -Heizkörper Vorlauf</t>
         </is>
+      </c>
+      <c r="H7" t="n">
+        <v>800</v>
       </c>
     </row>
   </sheetData>
